--- a/test-plan/Redmine_Test_Plan_and_Test_Cases.xlsx
+++ b/test-plan/Redmine_Test_Plan_and_Test_Cases.xlsx
@@ -173,7 +173,7 @@
     <t xml:space="preserve">2. Review search results.</t>
   </si>
   <si>
-    <t xml:space="preserve">At least one relevant result is displayed.</t>
+    <t xml:space="preserve">At least one search result is displayed.</t>
   </si>
   <si>
     <t xml:space="preserve">TC-004</t>
